--- a/Tables/for_paper_new_data.xlsx
+++ b/Tables/for_paper_new_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sccwrp-my.sharepoint.com/personal/katiei_sccwrp_org/Documents/Documents - Katie’s MacBook Pro/git/Irving_et_al_arroyo_toad/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="8_{09256A24-123F-B64E-BC00-9B9FEFFC0599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46CB8B2E-C852-DE40-ABEE-A8B1014D5197}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{09256A24-123F-B64E-BC00-9B9FEFFC0599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC72AEB-B429-5847-87CD-651BE635CC76}"/>
   <bookViews>
-    <workbookView xWindow="38840" yWindow="3420" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{A6C0AEEB-32FB-0A47-836B-0AB6323C08E0}"/>
+    <workbookView xWindow="5880" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{A6C0AEEB-32FB-0A47-836B-0AB6323C08E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 4" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="Rel importance" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">FFM!$A$1:$C$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">FFM!$A$1:$N$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="236">
   <si>
     <t>Mean</t>
   </si>
@@ -816,7 +817,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -826,6 +827,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -860,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -900,6 +907,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1368,7 +1379,7 @@
       <c r="D3" s="2">
         <v>1324.48841952869</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F3">
@@ -1438,7 +1449,7 @@
       <c r="D5" s="2">
         <v>1188.8835257185201</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="18">
         <v>0.01</v>
       </c>
       <c r="F5">
@@ -1508,7 +1519,7 @@
       <c r="D7" s="2">
         <v>1303.5536362103601</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F7">
@@ -1613,14 +1624,14 @@
       <c r="D10" s="2">
         <v>1171.70297285519</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F10">
-        <v>696</v>
+        <v>421</v>
       </c>
       <c r="G10" s="2">
-        <v>29.095792300805702</v>
+        <v>18.710832587287399</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>216</v>
@@ -1648,7 +1659,7 @@
       <c r="D11" s="2">
         <v>1306.7956098152299</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="18">
         <v>0.01</v>
       </c>
       <c r="F11">
@@ -1683,14 +1694,14 @@
       <c r="D12" s="2">
         <v>1222.8428590204901</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="18">
         <v>0.01</v>
       </c>
       <c r="F12">
-        <v>421</v>
+        <v>696</v>
       </c>
       <c r="G12" s="2">
-        <v>18.710832587287399</v>
+        <v>29.095792300805702</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>218</v>
@@ -1838,6 +1849,7 @@
       <c r="H32" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K12" xr:uid="{610C9C89-2AC8-B74E-8BC5-7A6F8B3BBCDF}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E4">
     <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
@@ -2605,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA29CDA0-60A2-9A4F-A861-5E644549F523}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.6640625" style="2" customWidth="1"/>
@@ -2651,7 +2663,7 @@
       <c r="C2">
         <v>2234</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>81.826320501342906</v>
       </c>
       <c r="E2">
@@ -2660,7 +2672,7 @@
       <c r="F2">
         <v>326</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>14.592658907788699</v>
       </c>
     </row>
@@ -2674,7 +2686,7 @@
       <c r="C3">
         <v>2234</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>94.449418084154004</v>
       </c>
       <c r="E3">
@@ -2683,7 +2695,7 @@
       <c r="F3">
         <v>-64</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>-2.8648164726947201</v>
       </c>
     </row>
@@ -2697,7 +2709,7 @@
       <c r="C4">
         <v>2234</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>29.230080572963299</v>
       </c>
       <c r="E4">
@@ -2706,7 +2718,7 @@
       <c r="F4">
         <v>1537</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>68.800358102059107</v>
       </c>
     </row>
@@ -2720,7 +2732,7 @@
       <c r="C5">
         <v>2234</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>95.926589077887201</v>
       </c>
       <c r="E5">
@@ -2729,7 +2741,7 @@
       <c r="F5">
         <v>-22</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>-0.98478066248880902</v>
       </c>
     </row>
@@ -2743,7 +2755,7 @@
       <c r="C6">
         <v>2234</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>65.935541629364394</v>
       </c>
       <c r="E6">
@@ -2752,7 +2764,7 @@
       <c r="F6">
         <v>638</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>28.5586392121755</v>
       </c>
     </row>
@@ -2766,7 +2778,7 @@
       <c r="C7">
         <v>2234</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>34.9597135183527</v>
       </c>
       <c r="E7">
@@ -2775,7 +2787,7 @@
       <c r="F7">
         <v>1392</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>62.309758281110099</v>
       </c>
     </row>
@@ -2789,7 +2801,7 @@
       <c r="C8">
         <v>2234</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>55.819158460161098</v>
       </c>
       <c r="E8">
@@ -2798,7 +2810,7 @@
       <c r="F8">
         <v>909</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>40.689346463742197</v>
       </c>
     </row>
@@ -2807,22 +2819,22 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>650</v>
+        <v>418</v>
       </c>
       <c r="C9">
         <v>2234</v>
       </c>
-      <c r="D9" s="2">
-        <v>29.095792300805702</v>
+      <c r="D9">
+        <v>18.710832587287399</v>
       </c>
       <c r="E9">
-        <v>696</v>
+        <v>421</v>
       </c>
       <c r="F9">
-        <v>1538</v>
-      </c>
-      <c r="G9" s="2">
-        <v>68.845120859444904</v>
+        <v>1813</v>
+      </c>
+      <c r="G9">
+        <v>81.154879140555096</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -2835,7 +2847,7 @@
       <c r="C10">
         <v>2234</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>63.607878245299901</v>
       </c>
       <c r="E10">
@@ -2844,7 +2856,7 @@
       <c r="F10">
         <v>712</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>31.871083258728699</v>
       </c>
     </row>
@@ -2853,23 +2865,200 @@
         <v>59</v>
       </c>
       <c r="B11">
-        <v>418</v>
+        <v>650</v>
       </c>
       <c r="C11">
         <v>2234</v>
       </c>
-      <c r="D11" s="2">
-        <v>18.710832587287399</v>
+      <c r="D11">
+        <v>29.095792300805702</v>
       </c>
       <c r="E11">
+        <v>696</v>
+      </c>
+      <c r="F11">
+        <v>1538</v>
+      </c>
+      <c r="G11">
+        <v>68.845120859444904</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15">
+        <v>1908</v>
+      </c>
+      <c r="C15">
+        <v>2234</v>
+      </c>
+      <c r="D15">
+        <v>326</v>
+      </c>
+      <c r="E15">
+        <v>14.592658907788699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>2298</v>
+      </c>
+      <c r="C16">
+        <v>2234</v>
+      </c>
+      <c r="D16">
+        <v>-64</v>
+      </c>
+      <c r="E16">
+        <v>-2.8648164726947201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>697</v>
+      </c>
+      <c r="C17">
+        <v>2234</v>
+      </c>
+      <c r="D17">
+        <v>1537</v>
+      </c>
+      <c r="E17">
+        <v>68.800358102059107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18">
+        <v>2256</v>
+      </c>
+      <c r="C18">
+        <v>2234</v>
+      </c>
+      <c r="D18">
+        <v>-22</v>
+      </c>
+      <c r="E18">
+        <v>-0.98478066248880902</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <v>1596</v>
+      </c>
+      <c r="C19">
+        <v>2234</v>
+      </c>
+      <c r="D19">
+        <v>638</v>
+      </c>
+      <c r="E19">
+        <v>28.5586392121755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20">
+        <v>842</v>
+      </c>
+      <c r="C20">
+        <v>2234</v>
+      </c>
+      <c r="D20">
+        <v>1392</v>
+      </c>
+      <c r="E20">
+        <v>62.309758281110099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21">
+        <v>1325</v>
+      </c>
+      <c r="C21">
+        <v>2234</v>
+      </c>
+      <c r="D21">
+        <v>909</v>
+      </c>
+      <c r="E21">
+        <v>40.689346463742197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22">
         <v>421</v>
       </c>
-      <c r="F11">
+      <c r="C22">
+        <v>2234</v>
+      </c>
+      <c r="D22">
         <v>1813</v>
       </c>
-      <c r="G11" s="2">
+      <c r="E22">
         <v>81.154879140555096</v>
       </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23">
+        <v>1522</v>
+      </c>
+      <c r="C23">
+        <v>2234</v>
+      </c>
+      <c r="D23">
+        <v>712</v>
+      </c>
+      <c r="E23">
+        <v>31.871083258728699</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>696</v>
+      </c>
+      <c r="C24">
+        <v>2234</v>
+      </c>
+      <c r="D24">
+        <v>1538</v>
+      </c>
+      <c r="E24">
+        <v>68.845120859444904</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4433,10 +4622,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F309909F-5A93-0A45-ADA8-6244FE0E89BD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -4453,7 +4644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4467,7 +4658,7 @@
         <v>4487.87039299147</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4481,7 +4672,7 @@
         <v>4466</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4496,7 +4687,7 @@
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4510,7 +4701,7 @@
         <v>4097.5524914761099</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -4524,7 +4715,7 @@
         <v>3200.9885634191301</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4539,7 +4730,7 @@
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -4553,7 +4744,7 @@
         <v>2728.2269461251799</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4567,7 +4758,7 @@
         <v>516.51270319792798</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4581,7 +4772,7 @@
         <v>1004.25693800316</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4596,7 +4787,7 @@
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -4611,7 +4802,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -4626,7 +4817,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -4640,7 +4831,7 @@
         <v>3576</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4654,7 +4845,7 @@
         <v>3582.3580633665201</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4771,7 +4962,7 @@
         <v>1043.23138300695</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4786,7 +4977,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4801,7 +4992,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -4816,7 +5007,7 @@
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -4933,7 +5124,7 @@
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -4948,7 +5139,7 @@
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -4963,7 +5154,7 @@
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -4977,7 +5168,7 @@
         <v>951.84284341632394</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -5093,7 +5284,7 @@
       <c r="I45" s="4"/>
       <c r="N45" s="4"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -5107,7 +5298,7 @@
         <v>198.34659140615</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -5121,7 +5312,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -5136,7 +5327,7 @@
       </c>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -5252,7 +5443,7 @@
         <v>20.552565179876801</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -5266,7 +5457,7 @@
         <v>3486.4556002254999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -5280,7 +5471,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -5294,7 +5485,7 @@
         <v>3289.0642142552001</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -5406,7 +5597,7 @@
         <v>1057.02899236039</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -5420,7 +5611,7 @@
         <v>2462.1694432835502</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -5434,7 +5625,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -5448,7 +5639,7 @@
         <v>2356.07255281481</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -5560,7 +5751,7 @@
         <v>626.42712139937805</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>22</v>
       </c>
@@ -5574,7 +5765,7 @@
         <v>2724.3493705793499</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>22</v>
       </c>
@@ -5588,7 +5779,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -5602,7 +5793,7 @@
         <v>2754.6272481460901</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -5714,7 +5905,7 @@
         <v>689.87696771066499</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>19</v>
       </c>
@@ -5728,7 +5919,7 @@
         <v>182.38200912475099</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -5742,7 +5933,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -5756,7 +5947,7 @@
         <v>108.41732785238101</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -5869,6 +6060,31 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N100" xr:uid="{F309909F-5A93-0A45-ADA8-6244FE0E89BD}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="DS_Mag_50"/>
+        <filter val="FA_Mag"/>
+        <filter val="Peak_10"/>
+        <filter val="Peak_2"/>
+        <filter val="Q99"/>
+        <filter val="SP_Mag"/>
+        <filter val="Wet_BFL_Mag_10"/>
+        <filter val="Wet_BFL_Mag_50"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Hotter"/>
+        <filter val="Large Perturbations, drier/hotter"/>
+        <filter val="Large Perturbations, extremes/hotter"/>
+        <filter val="Large Perturbations, wetter/hotter"/>
+        <filter val="Small Perturbations, drier/hotter"/>
+        <filter val="Small Perturbations, extremes/hotter"/>
+        <filter val="Small Perturbations, wetter/hotter"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B1 B56:B1048576">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0.05</formula>
